--- a/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>RequiredPoints</t>
   </si>
   <si>
-    <t>RewardItemId</t>
+    <t>RewardItem</t>
   </si>
   <si>
     <t>##type</t>
@@ -47,7 +47,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>(array#sep=,),int</t>
+    <t>(array#sep=@),rewardItem</t>
   </si>
   <si>
     <t>##</t>
@@ -59,37 +59,37 @@
     <t>奖励道具Id</t>
   </si>
   <si>
-    <t>10001001,10000002</t>
-  </si>
-  <si>
-    <t>10001003</t>
-  </si>
-  <si>
-    <t>10001004</t>
-  </si>
-  <si>
-    <t>10001005,10001006</t>
-  </si>
-  <si>
-    <t>10003001</t>
-  </si>
-  <si>
-    <t>10003002</t>
-  </si>
-  <si>
-    <t>10003003</t>
-  </si>
-  <si>
-    <t>10003004</t>
-  </si>
-  <si>
-    <t>10003005</t>
-  </si>
-  <si>
-    <t>10003006</t>
-  </si>
-  <si>
-    <t>10003011</t>
+    <t>10001001;1@10000002;1</t>
+  </si>
+  <si>
+    <t>10001003;1</t>
+  </si>
+  <si>
+    <t>10001004;1</t>
+  </si>
+  <si>
+    <t>10001005;1@10001006;1</t>
+  </si>
+  <si>
+    <t>10003001;1</t>
+  </si>
+  <si>
+    <t>10003002;1</t>
+  </si>
+  <si>
+    <t>10003003;1</t>
+  </si>
+  <si>
+    <t>10003004;1</t>
+  </si>
+  <si>
+    <t>10003005;1</t>
+  </si>
+  <si>
+    <t>10003006;1</t>
+  </si>
+  <si>
+    <t>10003011;1</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:4">
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:4">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:4">
       <c r="B14" s="2">
         <v>10002002</v>
       </c>

--- a/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
@@ -59,7 +59,7 @@
     <t>奖励道具Id</t>
   </si>
   <si>
-    <t>10001001;1@10000002;1</t>
+    <t>10001001;1@10001002;1</t>
   </si>
   <si>
     <t>10001003;1</t>

--- a/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ArchiveRewardConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1192,7 +1192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="2:4">
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="1:4">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B13" s="2">
         <v>10000010</v>
       </c>
@@ -1309,9 +1309,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="2:4">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="B14" s="2">
-        <v>10002002</v>
+        <v>10000011</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
